--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -417,7 +417,7 @@
     <t>DataEnterer.assignedEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity}
 </t>
   </si>
 </sst>
@@ -995,7 +995,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -1298,7 +1298,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1399,7 +1399,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1502,7 +1502,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1910,7 +1910,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2007,7 +2007,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>DataEnterer contient les informations relatives à l’opérateur de saisie de tout ou partie du contenu du 
-document.</t>
+    <t>DataEnterer contient les informations relatives à l’opérateur de saisie de tout ou partie du contenu du document.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="133">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>DataEnterer.typeId.nullFlavor</t>
@@ -1273,7 +1277,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1281,10 +1285,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1382,17 +1386,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1410,11 +1414,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1465,7 +1469,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1485,17 +1489,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1513,11 +1517,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1568,7 +1572,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1588,17 +1592,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1616,11 +1620,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1629,7 +1633,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1671,7 +1675,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1691,17 +1695,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1719,11 +1723,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1774,7 +1778,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1794,10 +1798,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1824,7 +1828,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1875,7 +1879,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1895,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1932,7 +1936,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1972,7 +1976,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -1992,10 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2029,7 +2033,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2051,7 +2055,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2069,7 +2073,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2089,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2115,7 +2119,7 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2168,7 +2172,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2188,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2214,7 +2218,7 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -2267,7 +2271,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="141">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -417,11 +417,36 @@
 </t>
   </si>
   <si>
+    <t>Horodatage de la participation de l’opérateur.</t>
+  </si>
+  <si>
+    <t>DataEnterer.time.nullFlavor</t>
+  </si>
+  <si>
+    <t>DataEnterer.time.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://hl7.org/cda/stds/core/StructureDefinition/ts-simple}
+</t>
+  </si>
+  <si>
+    <t>Date et heure à laquelle l’opérateur a participé à l’élaboration du document.</t>
+  </si>
+  <si>
+    <t>A quantity specifying a point on the axis of natural time. A point in time is most often represented as a calendar expression.</t>
+  </si>
+  <si>
+    <t>TS.value</t>
+  </si>
+  <si>
     <t>DataEnterer.assignedEntity</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity}
 </t>
+  </si>
+  <si>
+    <t>Personne physique.</t>
   </si>
 </sst>
 </file>
@@ -723,7 +748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.7890625" customWidth="true" bestFit="true"/>
@@ -2121,7 +2146,9 @@
       <c r="K14" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2192,18 +2219,20 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>75</v>
@@ -2218,10 +2247,12 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2247,13 +2278,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2271,10 +2300,10 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>75</v>
@@ -2286,6 +2315,210 @@
         <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>DataEnterer contient les informations relatives à l’opérateur de saisie de tout ou partie du contenu du document.</t>
+    <t>L'élément de l'en-tête du CDA dataEnterer contient les informations relatives à l’opérateur de saisie de tout ou partie du contenu du document.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
